--- a/examples/mascetti/decaf_2025.xlsx
+++ b/examples/mascetti/decaf_2025.xlsx
@@ -659,27 +659,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -700,75 +701,80 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
+          <t>Azienda</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
           <t>Descrizione</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Paese</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Acquisto</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Vendita</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Val. iniz. orig.</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Val. fin. orig.</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Cambio iniz.</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Cambio fin.</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>Val. iniz. EUR</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>Val. fin. EUR</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>Giorni</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>Quota %</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>IVAFE</t>
         </is>
@@ -790,57 +796,62 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>SPKZ (2024-01-12)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>100</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2024-01-12</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="K2" s="4" t="n">
         <v>1800</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.0389</v>
-      </c>
       <c r="M2" t="n">
+        <v>1.0389</v>
+      </c>
+      <c r="N2" t="n">
         <v>1.0912</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="O2" s="4" t="n">
         <v>1732.6</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="P2" s="4" t="n">
         <v>1832.84</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>70</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>100</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="S2" s="4" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -860,57 +871,62 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>MASCETTI CONTE AG</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>MSCT (2024-01-17)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>200</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2024-01-17</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="K3" s="4" t="n">
         <v>2800</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>3200</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="4" t="n">
         <v>2800</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="P3" s="4" t="n">
         <v>3200</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>252</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>100</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>4.42</v>
       </c>
     </row>
@@ -930,53 +946,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TAPPETINO STUZZICATO SPA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TPPC (2024-01-22)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>300</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2024-01-22</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" s="4" t="n">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" s="4" t="n">
         <v>2700</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>3000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="n">
         <v>2700</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="P4" s="4" t="n">
         <v>3000</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>365</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>100</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="S4" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -996,57 +1017,62 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>SPKZ (2024-02-14)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>100</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>2024-02-14</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2025-03-11</t>
         </is>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>1800</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>1800</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.0389</v>
+      <c r="L5" s="4" t="n">
+        <v>1800</v>
       </c>
       <c r="M5" t="n">
+        <v>1.0389</v>
+      </c>
+      <c r="N5" t="n">
         <v>1.0912</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="O5" s="4" t="n">
         <v>1732.6</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="P5" s="4" t="n">
         <v>1649.56</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>70</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>100</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="S5" s="4" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -1066,53 +1092,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>CLACSONATO A DESTRA CORP</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLCS (2024-02-22)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>100</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>2024-02-22</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" s="4" t="n">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" s="4" t="n">
         <v>2200</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>2500</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.0389</v>
-      </c>
       <c r="M6" t="n">
+        <v>1.0389</v>
+      </c>
+      <c r="N6" t="n">
         <v>1.175</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="O6" s="4" t="n">
         <v>2117.62</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="P6" s="4" t="n">
         <v>2127.66</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>365</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>100</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="S6" s="4" t="n">
         <v>4.26</v>
       </c>
     </row>
@@ -1132,53 +1163,58 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>STUZZICAPUOVA LLC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>STZC (2024-04-17)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>50</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2024-04-17</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" s="4" t="n">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>875</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.0389</v>
-      </c>
       <c r="M7" t="n">
+        <v>1.0389</v>
+      </c>
+      <c r="N7" t="n">
         <v>1.175</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="O7" s="4" t="n">
         <v>770.05</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="P7" s="4" t="n">
         <v>744.6799999999999</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>365</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>100</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="S7" s="4" t="n">
         <v>1.49</v>
       </c>
     </row>
@@ -1194,53 +1230,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SPRC (2024-05-17)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
         <v>25</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2024-05-17</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>2025-10-16</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>1300</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="L8" s="4" t="n">
         <v>1475</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.0389</v>
-      </c>
       <c r="M8" t="n">
+        <v>1.0389</v>
+      </c>
+      <c r="N8" t="n">
         <v>1.1649</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="O8" s="4" t="n">
         <v>1251.32</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="P8" s="4" t="n">
         <v>1266.2</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>289</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>100</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="S8" s="4" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -1256,53 +1297,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>SPRC (2024-08-17)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
         <v>20</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2024-08-17</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2025-10-16</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>1040</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="L9" s="4" t="n">
         <v>1200</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.0389</v>
-      </c>
       <c r="M9" t="n">
+        <v>1.0389</v>
+      </c>
+      <c r="N9" t="n">
         <v>1.1649</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="O9" s="4" t="n">
         <v>1001.06</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>1030.13</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>289</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>100</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>1.63</v>
       </c>
     </row>
@@ -1318,49 +1364,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>SPRC (2024-08-17)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
         <v>5</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2024-08-17</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" s="4" t="n">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" s="4" t="n">
         <v>260</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="L10" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.0389</v>
-      </c>
       <c r="M10" t="n">
+        <v>1.0389</v>
+      </c>
+      <c r="N10" t="n">
         <v>1.175</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="O10" s="4" t="n">
         <v>250.26</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="P10" s="4" t="n">
         <v>246.81</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>365</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>100</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>0.49</v>
       </c>
     </row>
@@ -1376,49 +1427,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SPRC (2024-11-17)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
         <v>25</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" s="4" t="n">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" s="4" t="n">
         <v>1300</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="L11" s="4" t="n">
         <v>1450</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.0389</v>
-      </c>
       <c r="M11" t="n">
+        <v>1.0389</v>
+      </c>
+      <c r="N11" t="n">
         <v>1.175</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="O11" s="4" t="n">
         <v>1251.32</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="P11" s="4" t="n">
         <v>1234.04</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>365</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>100</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>2.47</v>
       </c>
     </row>
@@ -1434,49 +1490,54 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>SPRC (2025-02-17)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
         <v>30</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2025-02-17</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" s="4" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" s="4" t="n">
         <v>1680</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="L12" s="4" t="n">
         <v>1740</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>1.0473</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1.175</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="O12" s="4" t="n">
         <v>1604.12</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="P12" s="4" t="n">
         <v>1480.85</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>318</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="S12" s="4" t="n">
         <v>2.58</v>
       </c>
     </row>
@@ -1496,53 +1557,58 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>ANTANI PREMATURATO CORP</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>ANTN (2025-04-22)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>100</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" s="4" t="n">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="L13" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>1.1476</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1.175</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="O13" s="4" t="n">
         <v>435.69</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="P13" s="4" t="n">
         <v>510.64</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>254</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>100</v>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>0.71</v>
       </c>
     </row>
@@ -1558,49 +1624,54 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SPRC (2025-05-17)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
         <v>30</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>2025-05-17</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" s="4" t="n">
-        <v>1740</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" s="4" t="n">
         <v>1740</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="4" t="n">
+        <v>1740</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.1194</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1.175</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="O14" s="4" t="n">
         <v>1554.4</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="P14" s="4" t="n">
         <v>1480.85</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>229</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>100</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="S14" s="4" t="n">
         <v>1.86</v>
       </c>
     </row>
@@ -1616,49 +1687,54 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>SPRC (2025-08-17)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
         <v>30</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" s="4" t="n">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" s="4" t="n">
         <v>1800</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="L15" s="4" t="n">
         <v>1740</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>1.1688</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>1.175</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="O15" s="4" t="n">
         <v>1540.04</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="P15" s="4" t="n">
         <v>1480.85</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>137</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>100</v>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="S15" s="4" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -1674,54 +1750,59 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>SUPERCAZZOLA PREMATURATA INC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>SPRC (2025-11-17)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="n">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
         <v>30</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2025-11-17</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" s="4" t="n">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" s="4" t="n">
         <v>1860</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="L16" s="4" t="n">
         <v>1740</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>1.1593</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>1.175</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="O16" s="4" t="n">
         <v>1604.42</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="P16" s="4" t="n">
         <v>1480.85</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>45</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>100</v>
       </c>
-      <c r="R16" s="4" t="n">
+      <c r="S16" s="4" t="n">
         <v>0.37</v>
       </c>
     </row>
     <row r="17">
-      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1732,12 +1813,12 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t>TOTALE</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -1745,7 +1826,8 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" s="4" t="n">
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" s="4" t="n">
         <v>30.73</v>
       </c>
     </row>
@@ -1760,21 +1842,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1790,50 +1873,55 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
+          <t>Azienda</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
           <t>Data acquisto</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Data vendita</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Corrispettivo EUR</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Costo EUR</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>+/- EUR</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Cambio BCE</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Forex</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>P/L broker</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>P/L broker EUR</t>
         </is>
@@ -1852,38 +1940,43 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>150</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="G2" s="4" t="n">
         <v>2749.27</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>1832.84</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>916.42</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1.0912</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="M2" s="4" t="n">
         <v>916.42</v>
       </c>
     </row>
@@ -1900,40 +1993,45 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>MASCETTI CONTE AG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>200</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="G3" s="4" t="n">
         <v>3200</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>2400</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>800</v>
       </c>
       <c r="L3" s="4" t="n">
         <v>800</v>
       </c>
+      <c r="M3" s="4" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1948,38 +2046,43 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>SPRC (acquired 2024-05-15)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2024-05-15</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>20</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>1030.13</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>858.4400000000001</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>171.69</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1.1649</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="M4" s="4" t="n">
         <v>171.69</v>
       </c>
     </row>
@@ -1996,38 +2099,43 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>SPRC (acquired 2024-08-15)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>2024-08-15</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>20</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>1030.13</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>892.78</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>137.35</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1.1649</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="L5" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="M5" s="4" t="n">
         <v>137.35</v>
       </c>
     </row>
@@ -2040,40 +2148,45 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Plusvalenza valutaria (FIFO USD)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>2024-02-07</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>13350</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>11773.53</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>12388.64</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>-615.12</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1.1339</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0</v>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
       <c r="L6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2084,40 +2197,45 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Plusvalenza valutaria (FIFO USD)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>44.1</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>46.49</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>-2.39</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1.1339</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0</v>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
       <c r="L7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2128,40 +2246,45 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Plusvalenza valutaria (FIFO USD)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>2400</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>2116.59</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>2236.72</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>-120.13</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>1.1339</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0</v>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
       <c r="L8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2172,40 +2295,45 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Plusvalenza valutaria (FIFO USD)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>2024-08-20</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>45</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>39.69</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>-0.91</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1.1339</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
       <c r="L9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2216,40 +2344,45 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Plusvalenza valutaria (FIFO USD)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1650</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>1455.15</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>1495.78</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>-40.63</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>1.1339</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
       <c r="L10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2260,40 +2393,45 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Plusvalenza valutaria (FIFO USD)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>40</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>35.28</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>37.8</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>-2.52</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>1.1339</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
       <c r="L11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2304,40 +2442,45 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Plusvalenza valutaria (FIFO USD)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>3000</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>2645.74</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>2749.27</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>-103.53</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>1.1339</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
       <c r="L12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2348,40 +2491,45 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Plusvalenza valutaria (FIFO USD)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>2025-04-03</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>59465</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>52442.9</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>53586.55</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>-1143.66</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>1.1339</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
       <c r="L13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2392,43 +2540,48 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Plusvalenza valutaria (FIFO USD)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>2025-04-03</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>2400</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>2066.83</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>2162.75</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="I14" s="4" t="n">
         <v>-95.92</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1.1612</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
       </c>
       <c r="L14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
-      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -2437,12 +2590,13 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>NETTO</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>-99.34999999999999</v>
       </c>
     </row>

--- a/examples/mascetti/decaf_2025.xlsx
+++ b/examples/mascetti/decaf_2025.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>-99.34999999999999</v>
+        <v>488.64</v>
       </c>
     </row>
     <row r="15">
@@ -1842,18 +1842,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
@@ -2148,12 +2148,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plusvalenza valutaria (FIFO USD)</t>
+          <t>Plusvalenza valutaria USD (LIFO per conto)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2162,16 +2162,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13350</v>
+        <v>80000</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11773.53</v>
+        <v>70552.96000000001</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>12388.64</v>
+        <v>72091.56</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-615.12</v>
+        <v>-1538.6</v>
       </c>
       <c r="J6" t="n">
         <v>1.1339</v>
@@ -2197,33 +2197,33 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plusvalenza valutaria (FIFO USD)</t>
+          <t>Plusvalenza valutaria USD (LIFO per conto)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>2400</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>44.1</v>
+        <v>2066.83</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>46.49</v>
+        <v>2065.05</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.39</v>
+        <v>1.78</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1339</v>
+        <v>1.1612</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2238,366 +2238,23 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EUR.USD</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Plusvalenza valutaria (FIFO USD)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>2116.59</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>2236.72</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>-120.13</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.1339</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EUR.USD</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Plusvalenza valutaria (FIFO USD)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2024-08-20</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>45</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>40.6</v>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NETTO</t>
+        </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.1339</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EUR.USD</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Plusvalenza valutaria (FIFO USD)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1650</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1455.15</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>1495.78</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>-40.63</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.1339</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>EUR.USD</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Plusvalenza valutaria (FIFO USD)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>40</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>35.28</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>-2.52</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.1339</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>EUR.USD</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Plusvalenza valutaria (FIFO USD)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>2645.74</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>2749.27</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>-103.53</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.1339</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>EUR.USD</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Plusvalenza valutaria (FIFO USD)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>59465</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>52442.9</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>53586.55</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>-1143.66</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.1339</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>EUR.USD</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Plusvalenza valutaria (FIFO USD)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>2400</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>2066.83</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>2162.75</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>-95.92</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.1612</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="I15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>NETTO</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>-99.34999999999999</v>
+        <v>488.64</v>
       </c>
     </row>
   </sheetData>

--- a/examples/mascetti/decaf_2025.xlsx
+++ b/examples/mascetti/decaf_2025.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>488.64</v>
+        <v>486.86</v>
       </c>
     </row>
     <row r="15">
@@ -1842,7 +1842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2189,72 +2189,23 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EUR.USD</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Plusvalenza valutaria USD (LIFO per conto)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2400</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>2066.83</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>2065.05</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.1612</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>NETTO</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n">
-        <v>488.64</v>
+      <c r="I8" s="4" t="n">
+        <v>486.86</v>
       </c>
     </row>
   </sheetData>
@@ -8977,10 +8928,10 @@
         </is>
       </c>
       <c r="B304" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C304" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D304" t="n">
         <v>1.0389</v>
@@ -8999,10 +8950,10 @@
         </is>
       </c>
       <c r="B305" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C305" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D305" t="n">
         <v>1.0389</v>
@@ -9021,10 +8972,10 @@
         </is>
       </c>
       <c r="B306" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C306" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D306" t="n">
         <v>1.0389</v>
@@ -9043,10 +8994,10 @@
         </is>
       </c>
       <c r="B307" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C307" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D307" t="n">
         <v>1.0389</v>
@@ -9065,10 +9016,10 @@
         </is>
       </c>
       <c r="B308" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C308" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D308" t="n">
         <v>1.0389</v>
@@ -9087,10 +9038,10 @@
         </is>
       </c>
       <c r="B309" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C309" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D309" t="n">
         <v>1.0389</v>
@@ -9105,10 +9056,10 @@
         </is>
       </c>
       <c r="B310" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C310" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D310" t="n">
         <v>1.0389</v>
@@ -9123,10 +9074,10 @@
         </is>
       </c>
       <c r="B311" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C311" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D311" t="n">
         <v>1.0389</v>
@@ -9145,10 +9096,10 @@
         </is>
       </c>
       <c r="B312" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C312" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D312" t="n">
         <v>1.0389</v>
@@ -9167,10 +9118,10 @@
         </is>
       </c>
       <c r="B313" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C313" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D313" t="n">
         <v>1.0389</v>
@@ -9189,10 +9140,10 @@
         </is>
       </c>
       <c r="B314" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C314" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D314" t="n">
         <v>1.0389</v>
@@ -9211,10 +9162,10 @@
         </is>
       </c>
       <c r="B315" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C315" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D315" t="n">
         <v>1.0389</v>
@@ -9233,10 +9184,10 @@
         </is>
       </c>
       <c r="B316" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C316" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D316" t="n">
         <v>1.0389</v>
@@ -9251,10 +9202,10 @@
         </is>
       </c>
       <c r="B317" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C317" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D317" t="n">
         <v>1.0389</v>
@@ -9269,10 +9220,10 @@
         </is>
       </c>
       <c r="B318" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C318" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D318" t="n">
         <v>1.0389</v>
@@ -9291,10 +9242,10 @@
         </is>
       </c>
       <c r="B319" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C319" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D319" t="n">
         <v>1.0389</v>
@@ -9313,10 +9264,10 @@
         </is>
       </c>
       <c r="B320" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C320" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D320" t="n">
         <v>1.0389</v>
@@ -9335,10 +9286,10 @@
         </is>
       </c>
       <c r="B321" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C321" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D321" t="n">
         <v>1.0389</v>
@@ -9357,10 +9308,10 @@
         </is>
       </c>
       <c r="B322" s="4" t="n">
-        <v>13708.5</v>
+        <v>16108.5</v>
       </c>
       <c r="C322" s="4" t="n">
-        <v>13195.20646838002</v>
+        <v>15505.3421888536</v>
       </c>
       <c r="D322" t="n">
         <v>1.0389</v>
@@ -9379,10 +9330,10 @@
         </is>
       </c>
       <c r="B323" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C323" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D323" t="n">
         <v>1.0389</v>
@@ -9397,10 +9348,10 @@
         </is>
       </c>
       <c r="B324" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C324" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D324" t="n">
         <v>1.0389</v>
@@ -9415,10 +9366,10 @@
         </is>
       </c>
       <c r="B325" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C325" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D325" t="n">
         <v>1.0389</v>
@@ -9437,10 +9388,10 @@
         </is>
       </c>
       <c r="B326" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C326" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D326" t="n">
         <v>1.0389</v>
@@ -9459,10 +9410,10 @@
         </is>
       </c>
       <c r="B327" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C327" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D327" t="n">
         <v>1.0389</v>
@@ -9481,10 +9432,10 @@
         </is>
       </c>
       <c r="B328" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C328" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D328" t="n">
         <v>1.0389</v>
@@ -9503,10 +9454,10 @@
         </is>
       </c>
       <c r="B329" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C329" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D329" t="n">
         <v>1.0389</v>
@@ -9525,10 +9476,10 @@
         </is>
       </c>
       <c r="B330" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C330" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D330" t="n">
         <v>1.0389</v>
@@ -9543,10 +9494,10 @@
         </is>
       </c>
       <c r="B331" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C331" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D331" t="n">
         <v>1.0389</v>
@@ -9561,10 +9512,10 @@
         </is>
       </c>
       <c r="B332" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C332" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D332" t="n">
         <v>1.0389</v>
@@ -9583,10 +9534,10 @@
         </is>
       </c>
       <c r="B333" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C333" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D333" t="n">
         <v>1.0389</v>
@@ -9605,10 +9556,10 @@
         </is>
       </c>
       <c r="B334" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C334" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D334" t="n">
         <v>1.0389</v>
@@ -9627,10 +9578,10 @@
         </is>
       </c>
       <c r="B335" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C335" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D335" t="n">
         <v>1.0389</v>
@@ -9649,10 +9600,10 @@
         </is>
       </c>
       <c r="B336" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C336" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D336" t="n">
         <v>1.0389</v>
@@ -9671,10 +9622,10 @@
         </is>
       </c>
       <c r="B337" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C337" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D337" t="n">
         <v>1.0389</v>
@@ -9689,10 +9640,10 @@
         </is>
       </c>
       <c r="B338" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C338" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D338" t="n">
         <v>1.0389</v>
@@ -9707,10 +9658,10 @@
         </is>
       </c>
       <c r="B339" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C339" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D339" t="n">
         <v>1.0389</v>
@@ -9729,10 +9680,10 @@
         </is>
       </c>
       <c r="B340" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C340" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D340" t="n">
         <v>1.0389</v>
@@ -9751,10 +9702,10 @@
         </is>
       </c>
       <c r="B341" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C341" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D341" t="n">
         <v>1.0389</v>
@@ -9773,10 +9724,10 @@
         </is>
       </c>
       <c r="B342" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C342" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D342" t="n">
         <v>1.0389</v>
@@ -9795,10 +9746,10 @@
         </is>
       </c>
       <c r="B343" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C343" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D343" t="n">
         <v>1.0389</v>
@@ -9817,10 +9768,10 @@
         </is>
       </c>
       <c r="B344" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C344" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D344" t="n">
         <v>1.0389</v>
@@ -9835,10 +9786,10 @@
         </is>
       </c>
       <c r="B345" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C345" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D345" t="n">
         <v>1.0389</v>
@@ -9853,10 +9804,10 @@
         </is>
       </c>
       <c r="B346" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C346" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D346" t="n">
         <v>1.0389</v>
@@ -9871,10 +9822,10 @@
         </is>
       </c>
       <c r="B347" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C347" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D347" t="n">
         <v>1.0389</v>
@@ -9893,10 +9844,10 @@
         </is>
       </c>
       <c r="B348" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C348" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D348" t="n">
         <v>1.0389</v>
@@ -9915,10 +9866,10 @@
         </is>
       </c>
       <c r="B349" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C349" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D349" t="n">
         <v>1.0389</v>
@@ -9937,10 +9888,10 @@
         </is>
       </c>
       <c r="B350" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C350" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D350" t="n">
         <v>1.0389</v>
@@ -9959,10 +9910,10 @@
         </is>
       </c>
       <c r="B351" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C351" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D351" t="n">
         <v>1.0389</v>
@@ -9977,10 +9928,10 @@
         </is>
       </c>
       <c r="B352" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C352" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D352" t="n">
         <v>1.0389</v>
@@ -9995,10 +9946,10 @@
         </is>
       </c>
       <c r="B353" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C353" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D353" t="n">
         <v>1.0389</v>
@@ -10017,10 +9968,10 @@
         </is>
       </c>
       <c r="B354" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C354" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D354" t="n">
         <v>1.0389</v>
@@ -10039,10 +9990,10 @@
         </is>
       </c>
       <c r="B355" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C355" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D355" t="n">
         <v>1.0389</v>
@@ -10061,10 +10012,10 @@
         </is>
       </c>
       <c r="B356" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C356" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D356" t="n">
         <v>1.0389</v>
@@ -10083,10 +10034,10 @@
         </is>
       </c>
       <c r="B357" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C357" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D357" t="n">
         <v>1.0389</v>
@@ -10105,10 +10056,10 @@
         </is>
       </c>
       <c r="B358" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C358" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D358" t="n">
         <v>1.0389</v>
@@ -10123,10 +10074,10 @@
         </is>
       </c>
       <c r="B359" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C359" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D359" t="n">
         <v>1.0389</v>
@@ -10141,10 +10092,10 @@
         </is>
       </c>
       <c r="B360" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C360" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D360" t="n">
         <v>1.0389</v>
@@ -10163,10 +10114,10 @@
         </is>
       </c>
       <c r="B361" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C361" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D361" t="n">
         <v>1.0389</v>
@@ -10185,10 +10136,10 @@
         </is>
       </c>
       <c r="B362" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C362" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D362" t="n">
         <v>1.0389</v>
@@ -10207,10 +10158,10 @@
         </is>
       </c>
       <c r="B363" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C363" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D363" t="n">
         <v>1.0389</v>
@@ -10225,10 +10176,10 @@
         </is>
       </c>
       <c r="B364" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C364" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D364" t="n">
         <v>1.0389</v>
@@ -10243,10 +10194,10 @@
         </is>
       </c>
       <c r="B365" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C365" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D365" t="n">
         <v>1.0389</v>
@@ -10261,10 +10212,10 @@
         </is>
       </c>
       <c r="B366" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C366" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D366" t="n">
         <v>1.0389</v>
@@ -10279,10 +10230,10 @@
         </is>
       </c>
       <c r="B367" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C367" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D367" t="n">
         <v>1.0389</v>
@@ -10301,10 +10252,10 @@
         </is>
       </c>
       <c r="B368" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C368" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D368" t="n">
         <v>1.0389</v>
@@ -10323,10 +10274,10 @@
         </is>
       </c>
       <c r="B369" s="4" t="n">
-        <v>13758.5</v>
+        <v>16158.5</v>
       </c>
       <c r="C369" s="4" t="n">
-        <v>13243.33429588988</v>
+        <v>15553.47001636346</v>
       </c>
       <c r="D369" t="n">
         <v>1.0389</v>

--- a/examples/mascetti/decaf_2025.xlsx
+++ b/examples/mascetti/decaf_2025.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>486.86</v>
+        <v>357.14</v>
       </c>
     </row>
     <row r="15">
@@ -786,73 +786,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GB0000000100</t>
+          <t>DE0000000110</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SPKZ</t>
+          <t>MSCT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
+          <t>MASCETTI CONTE AG</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SPKZ (2024-01-12)</t>
+          <t>MSCT (2024-01-17)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1800</v>
+        <v>2800</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0389</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0912</v>
+        <v>1</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>1732.6</v>
+        <v>2800</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>1832.84</v>
+        <v>3200</v>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
+        <v>252</v>
       </c>
       <c r="R2" t="n">
         <v>100</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.7</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="3">
@@ -861,22 +861,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DE0000000110</t>
+          <t>IT0000000130</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MSCT</t>
+          <t>TPPC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MASCETTI CONTE AG</t>
+          <t>TAPPETINO STUZZICATO SPA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MSCT (2024-01-17)</t>
+          <t>TPPC (2024-01-22)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -886,27 +886,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
+          <t>2024-01-22</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" s="4" t="n">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -915,19 +911,19 @@
         <v>1</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="Q3" t="n">
-        <v>252</v>
+        <v>365</v>
       </c>
       <c r="R3" t="n">
         <v>100</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>4.42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -936,69 +932,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IT0000000130</t>
+          <t>GB0000000100</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TPPC</t>
+          <t>SPKZ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TAPPETINO STUZZICATO SPA</t>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TPPC (2024-01-22)</t>
+          <t>SPKZ (2024-02-14)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="n">
-        <v>2700</v>
+        <v>1800</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>1.0389</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>1.0912</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>2700</v>
+        <v>1732.6</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>3000</v>
+        <v>1649.56</v>
       </c>
       <c r="Q4" t="n">
-        <v>365</v>
+        <v>70</v>
       </c>
       <c r="R4" t="n">
         <v>100</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>6</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="5">
@@ -1007,22 +1007,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GB0000000100</t>
+          <t>US0000000120</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SPKZ</t>
+          <t>CLCS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
+          <t>CLACSONATO A DESTRA CORP</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SPKZ (2024-02-14)</t>
+          <t>CLCS (2024-02-22)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1040,40 +1040,36 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" s="4" t="n">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1800</v>
+        <v>2500</v>
       </c>
       <c r="M5" t="n">
         <v>1.0389</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0912</v>
+        <v>1.175</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>1732.6</v>
+        <v>2117.62</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>1649.56</v>
+        <v>2127.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>70</v>
+        <v>365</v>
       </c>
       <c r="R5" t="n">
         <v>100</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.63</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="6">
@@ -1082,22 +1078,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>US0000000120</t>
+          <t>GB0000000100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLCS</t>
+          <t>SPKZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CLACSONATO A DESTRA CORP</t>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CLCS (2024-02-22)</t>
+          <t>SPKZ (2024-04-12)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1107,7 +1103,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1115,36 +1111,40 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
       <c r="K6" s="4" t="n">
-        <v>2200</v>
+        <v>1800</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="M6" t="n">
         <v>1.0389</v>
       </c>
       <c r="N6" t="n">
-        <v>1.175</v>
+        <v>1.0912</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2117.62</v>
+        <v>1732.6</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2127.66</v>
+        <v>1832.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>365</v>
+        <v>70</v>
       </c>
       <c r="R6" t="n">
         <v>100</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>4.26</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7">
@@ -1842,7 +1842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1945,25 +1945,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2749.27</v>
+        <v>916.42</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1832.84</v>
+        <v>556.95</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>916.42</v>
+        <v>359.47</v>
       </c>
       <c r="J2" t="n">
         <v>1.0912</v>
@@ -1974,52 +1974,52 @@
         </is>
       </c>
       <c r="L2" s="4" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>916.42</v>
+        <v>366.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MSCT</t>
+          <t>SPKZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DE0000000110</t>
+          <t>GB0000000100</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MASCETTI CONTE AG</t>
+          <t>SPIKEZUCCHERI PREMATURATA PLC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>3200</v>
+        <v>1832.84</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2400</v>
+        <v>1289.13</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>800</v>
+        <v>543.71</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>1.0912</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2027,52 +2027,52 @@
         </is>
       </c>
       <c r="L3" s="4" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>800</v>
+        <v>549.85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SPRC</t>
+          <t>MSCT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>US13579C2467</t>
+          <t>DE0000000110</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SPRC (acquired 2024-05-15)</t>
+          <t>MASCETTI CONTE AG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-01-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1030.13</v>
+        <v>3200</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>858.4400000000001</v>
+        <v>2400</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>171.69</v>
+        <v>800</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1649</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>171.69</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5">
@@ -2099,17 +2099,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SPRC (acquired 2024-08-15)</t>
+          <t>SPRC (acquired 2024-05-15)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2119,10 +2119,10 @@
         <v>1030.13</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>892.78</v>
+        <v>923.1900000000001</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>137.35</v>
+        <v>106.94</v>
       </c>
       <c r="J5" t="n">
         <v>1.1649</v>
@@ -2133,79 +2133,132 @@
         </is>
       </c>
       <c r="L5" s="4" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>137.35</v>
+        <v>171.69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>SPRC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>US13579C2467</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SPRC (acquired 2024-08-15)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1030.13</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>944.51</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>85.62</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.1649</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>137.35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>EUR.USD</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Plusvalenza valutaria USD (LIFO per conto)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>2025-04-03</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>80000</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>70552.96000000001</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>72091.56</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>-1538.6</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>1.1339</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="I7" s="6" t="n"/>
-    </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="I8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>NETTO</t>
         </is>
       </c>
-      <c r="I8" s="4" t="n">
-        <v>486.86</v>
+      <c r="I9" s="4" t="n">
+        <v>357.14</v>
       </c>
     </row>
   </sheetData>

--- a/examples/mascetti/decaf_2025.xlsx
+++ b/examples/mascetti/decaf_2025.xlsx
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="L5" s="4" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>171.69</v>
+        <v>137.35</v>
       </c>
     </row>
     <row r="6">
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>137.35</v>
+        <v>103.01</v>
       </c>
     </row>
     <row r="7">

--- a/examples/mascetti/decaf_2025.xlsx
+++ b/examples/mascetti/decaf_2025.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,10 @@
     <font>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,12 +72,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -443,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -648,7 +653,47 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Controllo coerenza RSU (art. 9 c. 4 TUIR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Vest events nell'anno</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Reddito RSU tassato (EUR)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>6295.89</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Cross-check: deve essere sottoinsieme del punto 1 CU "Redditi di lavoro dipendente". Differenza = stipendio + bonus.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A27:D27"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -684,97 +729,97 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Cod.</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Simbolo</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Azienda</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Descrizione</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Paese</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Acquisto</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Vendita</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Val. iniz. orig.</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Val. fin. orig.</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Cambio iniz.</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Cambio fin.</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Val. iniz. EUR</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Val. fin. EUR</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>Giorni</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>Quota %</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>IVAFE</t>
         </is>
@@ -1802,7 +1847,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="S17" s="6" t="n"/>
+      <c r="S17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1861,67 +1906,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Simbolo</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Azienda</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Data acquisto</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Data vendita</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Corrispettivo EUR</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Costo EUR</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>+/- EUR</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Cambio BCE</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Forex</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>P/L broker</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>P/L broker EUR</t>
         </is>
@@ -2242,7 +2287,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -2285,37 +2330,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Descrizione</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Lordo</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Lordo EUR</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Ritenuta</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Ritenuta EUR</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Netto EUR</t>
         </is>
@@ -2430,9 +2475,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -2509,32 +2554,32 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Saldo USD</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Equiv. EUR</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Giorno lavorativo</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Sopra soglia</t>
         </is>
